--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -29,10 +29,7 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -43,12 +40,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001C1C1C"/>
+        <fgColor rgb="0019473C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,16 +59,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0E0DC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0E0DC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0E0DC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D0E0DC"/>
       </bottom>
     </border>
   </borders>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (26 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (28 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0004A"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,440 +488,474 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tenders@comcare.gov.au</t>
+          <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Comcare Australia</t>
+          <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>ictprofessionalservicespanel@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Australian Taxation Office</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>tenders@comcare.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Comcare Australia</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0004A"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,442 +508,442 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (28 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (30 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0004A"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,474 +488,508 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Export Finance and Insurance Corp</t>
+          <t>Bureau of Meteorology</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>contracts.its@anu.edu.au</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Australian National University</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>procurement@exportfinance.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Export Finance and Insurance Corp</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (30 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (36 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,11 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <color rgb="00C0004A"/>
     </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -49,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -503,17 +503,17 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>contracts.its@anu.edu.au</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Australian National University</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>procurementpanels@csiro.au</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Commonwealth Scientific and Industrial Research Organisation</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -522,474 +522,576 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>procurement@afsa.gov.au</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Export Finance and Insurance Corp</t>
+          <t>Australian Financial Security Authority</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ictprofessionalservicespanel@ato.gov.au</t>
+          <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>tenders@comcare.gov.au</t>
+          <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Comcare Australia</t>
+          <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>tenders@austrade.gov.au</t>
+          <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Australian Trade and Investment Commission</t>
+          <t>Defence Housing Australia</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>elliot.mendick@airservicesaustralia.com</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Airservices Australia</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>contracts.its@anu.edu.au</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Australian National University</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement@exportfinance.gov.au</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Export Finance and Insurance Corp</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ictprofessionalservicespanel@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Australian Taxation Office</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>tenders@comcare.gov.au</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Comcare Australia</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>tenders@austrade.gov.au</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Australian Trade and Investment Commission</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (36 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (41 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,11 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font/>
     <font>
       <b val="1"/>
       <color rgb="00C0004A"/>
     </font>
+    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -49,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -488,97 +488,97 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
+          <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Bureau of Meteorology</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>procurementpanels@csiro.au</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Commonwealth Scientific and Industrial Research Organisation</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>immunisation.handbook@cdc.gov.au</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>procurement@afsa.gov.au</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Australian Financial Security Authority</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>digitalprocurement@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>julie.dhakal@pmc.gov.au</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Department of the Prime Minister and Cabinet</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>cio@opc.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Office of Parliamentary Counsel</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>itbotenders@asic.gov.au</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Australian Securities &amp; Investments Commission</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>anil.acharya@aph.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Department of Parliamentary Services</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ictprocurement@dha.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Defence Housing Australia</t>
+          <t>Bureau of Meteorology</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -590,508 +590,593 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>procurementpanels@csiro.au</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Commonwealth Scientific and Industrial Research Organisation</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>procurement@afsa.gov.au</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Australian Financial Security Authority</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>julie.dhakal@pmc.gov.au</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Department of the Prime Minister and Cabinet</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>itbotenders@asic.gov.au</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Australian Securities &amp; Investments Commission</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ictprocurement@dha.gov.au</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Defence Housing Australia</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0004A"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -571,612 +559,612 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (41 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (45 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0004A"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,695 +488,763 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tracey.laba@health.gov.au</t>
+          <t>procurement@anao.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Australian National Audit Office</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>immunisation.handbook@cdc.gov.au</t>
+          <t>it.procurement@homeaffairs.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
+          <t>Department of Home Affairs</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>digitalprocurement@health.gov.au</t>
+          <t>ictprocurement@mdba.gov.au</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Murray-Darling Basin Authority</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>cop31procurement@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>tracey.laba@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>immunisation.handbook@cdc.gov.au</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>digitalprocurement@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0004A"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,697 +542,697 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (45 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (49 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0004A"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,763 +488,831 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>procurement@anao.gov.au</t>
+          <t>mathew.ford@homeaffairs.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Australian National Audit Office</t>
+          <t>Department of Home Affairs</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>it.procurement@homeaffairs.gov.au</t>
+          <t>it.procurement@accc.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Department of Home Affairs</t>
+          <t>Australian Competition and Consumer Commission</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ictprocurement@mdba.gov.au</t>
+          <t>bdas@heath.gov.au</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Murray-Darling Basin Authority</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>bdas@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>procurement@anao.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Australian National Audit Office</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>it.procurement@homeaffairs.gov.au</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Department of Home Affairs</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ictprocurement@mdba.gov.au</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Murray-Darling Basin Authority</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0004A"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,765 +542,765 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>procurement@anao.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Australian National Audit Office</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>it.procurement@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@mdba.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Murray-Darling Basin Authority</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (49 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (52 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0004A"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,831 +488,882 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>mathew.ford@homeaffairs.gov.au</t>
+          <t>tina.mackerness@airservicesaustralia.com</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Department of Home Affairs</t>
+          <t>Airservices Australia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>it.procurement@accc.gov.au</t>
+          <t>procurement@aciar.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Australian Competition and Consumer Commission</t>
+          <t>Australian Centre for International Agriculture Research</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>ict.panel.dmp@servicesaustralia.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Services Australia</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>mathew.ford@homeaffairs.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Department of Home Affairs</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>it.procurement@accc.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Australian Competition and Consumer Commission</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>bdas@heath.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>bdas@health.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>procurement@anao.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Australian National Audit Office</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>it.procurement@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>ictprocurement@mdba.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Murray-Darling Basin Authority</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (52 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (53 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -488,49 +488,49 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>procurementnqsc@ndiscommission.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NDIS Quality and Safeguards Commission</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>tina.mackerness@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Australian Centre for International Agriculture Research</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ict.panel.dmp@servicesaustralia.gov.au</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Services Australia</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
@@ -539,29 +539,29 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>mathew.ford@homeaffairs.gov.au</t>
+          <t>ict.panel.dmp@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Department of Home Affairs</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>it.procurement@accc.gov.au</t>
+          <t>mathew.ford@homeaffairs.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Australian Competition and Consumer Commission</t>
+          <t>Department of Home Affairs</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -573,12 +573,12 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>bdas@heath.gov.au</t>
+          <t>it.procurement@accc.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Australian Competition and Consumer Commission</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>bdas@health.gov.au</t>
+          <t>bdas@heath.gov.au</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -607,29 +607,29 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>procurement@anao.gov.au</t>
+          <t>bdas@health.gov.au</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Australian National Audit Office</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>it.procurement@homeaffairs.gov.au</t>
+          <t>procurement@anao.gov.au</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Department of Home Affairs</t>
+          <t>Australian National Audit Office</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -641,12 +641,12 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ictprocurement@mdba.gov.au</t>
+          <t>it.procurement@homeaffairs.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Murray-Darling Basin Authority</t>
+          <t>Department of Home Affairs</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
+          <t>ictprocurement@mdba.gov.au</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water</t>
+          <t>Murray-Darling Basin Authority</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -675,29 +675,29 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>tracey.laba@health.gov.au</t>
+          <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>immunisation.handbook@cdc.gov.au</t>
+          <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>digitalprocurement@health.gov.au</t>
+          <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -726,12 +726,12 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>cio@opc.gov.au</t>
+          <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Office of Parliamentary Counsel</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>anil.acharya@aph.gov.au</t>
+          <t>cio@opc.gov.au</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Department of Parliamentary Services</t>
+          <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -760,29 +760,29 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
+          <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Bureau of Meteorology</t>
+          <t>Department of Parliamentary Services</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>procurementpanels@csiro.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Commonwealth Scientific and Industrial Research Organisation</t>
+          <t>Bureau of Meteorology</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>procurement@afsa.gov.au</t>
+          <t>procurementpanels@csiro.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Australian Financial Security Authority</t>
+          <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>julie.dhakal@pmc.gov.au</t>
+          <t>procurement@afsa.gov.au</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Department of the Prime Minister and Cabinet</t>
+          <t>Australian Financial Security Authority</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -828,12 +828,12 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>itbotenders@asic.gov.au</t>
+          <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Australian Securities &amp; Investments Commission</t>
+          <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -845,12 +845,12 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ictprocurement@dha.gov.au</t>
+          <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Defence Housing Australia</t>
+          <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -862,12 +862,12 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>elliot.mendick@airservicesaustralia.com</t>
+          <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Airservices Australia</t>
+          <t>Defence Housing Australia</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>contracts.its@anu.edu.au</t>
+          <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Australian National University</t>
+          <t>Airservices Australia</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -896,29 +896,29 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Export Finance and Insurance Corp</t>
+          <t>Australian National University</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ictprofessionalservicespanel@ato.gov.au</t>
+          <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -930,29 +930,29 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>tenders@comcare.gov.au</t>
+          <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Comcare Australia</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>tenders@austrade.gov.au</t>
+          <t>tenders@comcare.gov.au</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Australian Trade and Investment Commission</t>
+          <t>Comcare Australia</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>spt@dfat.gov.au</t>
+          <t>tenders@austrade.gov.au</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs &amp; Trade</t>
+          <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -981,12 +981,12 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>procurement@austrac.gov.au</t>
+          <t>spt@dfat.gov.au</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
+          <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>procurement@apra.gov.au</t>
+          <t>procurement@austrac.gov.au</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Australian Prudential Regulation Authority</t>
+          <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>performancepsychologylead@ausport.gov.au</t>
+          <t>procurement@apra.gov.au</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Australian Sports Commission</t>
+          <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1032,12 +1032,12 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>msw@infrastructure.gov.au</t>
+          <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Australian Sports Commission</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>mitchell.howarth@pmc.gov.au</t>
+          <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Department of the Prime Minister and Cabinet</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>mattison.aquilina@pmc.gov.au</t>
+          <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>itd.labour.hire.services@health.gov.au</t>
+          <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1100,12 +1100,12 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>isd.contractors@aff.gov.au</t>
+          <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Department of Agriculture, Fisheries and Forestry</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1117,12 +1117,12 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>imtcgdmp2@csiro.au</t>
+          <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Commonwealth Scientific and Industrial Research Organisation</t>
+          <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1134,12 +1134,12 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ictsourcing@industry.gov.au</t>
+          <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1151,12 +1151,12 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ictsourcing@acic.gov.au</t>
+          <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Australian Crime Commission</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1168,12 +1168,12 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ictlabourhire@dcceew.gov.au</t>
+          <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water</t>
+          <t>Australian Crime Commission</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1185,12 +1185,12 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>grace.corr@ato.gov.au</t>
+          <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1202,12 +1202,12 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>gavin.stevenson@measurement.gov.au</t>
+          <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>dtddprocurementcomm@health.gov.au</t>
+          <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>dtdd.labourhire@health.gov.au</t>
+          <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1253,12 +1253,12 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>dbdprocurement@aff.gov.au</t>
+          <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Department of Agriculture, Fisheries and Forestry</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>corporate.procurements@grdc.com.au</t>
+          <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Grains Research &amp; Development Corporation</t>
+          <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1287,12 +1287,12 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>cio-it-labourhire@afp.gov.au</t>
+          <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Australian Federal Police</t>
+          <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>cdc.ict.labourhire@cdc.gov.au</t>
+          <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
+          <t>Australian Federal Police</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>bilal.arshad@act.gov.au</t>
+          <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>City and Environment Directorate</t>
+          <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -1338,12 +1338,12 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>aidan.chalker@nhmrc.gov.au</t>
+          <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>National Health and Medical Research Council</t>
+          <t>City and Environment Directorate</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1355,15 +1355,32 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
+          <t>aidan.chalker@nhmrc.gov.au</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>National Health and Medical Research Council</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/buyict_email_registry.xlsx
+++ b/buyict_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0004A"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019473C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -503,884 +491,884 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>tina.mackerness@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Australian Centre for International Agriculture Research</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ict.panel.dmp@servicesaustralia.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>mathew.ford@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>it.procurement@accc.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Australian Competition and Consumer Commission</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>bdas@heath.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>bdas@health.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>procurement@anao.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Australian National Audit Office</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>it.procurement@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@mdba.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Murray-Darling Basin Authority</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>tracey.laba@health.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>immunisation.handbook@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>digitalprocurement@health.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>cio@opc.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>anil.acharya@aph.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Department of Parliamentary Services</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Bureau of Meteorology</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>procurementpanels@csiro.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>procurement@afsa.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Australian Financial Security Authority</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>julie.dhakal@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>itbotenders@asic.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Australian Securities &amp; Investments Commission</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ictprocurement@dha.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>elliot.mendick@airservicesaustralia.com</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Airservices Australia</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>contracts.its@anu.edu.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Australian National University</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Export Finance and Insurance Corp</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>ictprofessionalservicespanel@ato.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>tenders@comcare.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Comcare Australia</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>tenders@austrade.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Australian Trade and Investment Commission</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>spt@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs &amp; Trade</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>procurement@austrac.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Australian Transaction Reports &amp; Analysis Centre (AUSTRAC)</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>procurement@apra.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Australian Prudential Regulation Authority</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>performancepsychologylead@ausport.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Australian Sports Commission</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>msw@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>mitchell.howarth@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>mattison.aquilina@pmc.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of the Prime Minister and Cabinet</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>itd.labour.hire.services@health.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>isd.contractors@aff.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>imtcgdmp2@csiro.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@industry.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>ictsourcing@acic.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Australian Crime Commission</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>ictlabourhire@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>grace.corr@ato.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>gavin.stevenson@measurement.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>dtddprocurementcomm@health.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>dtdd.labourhire@health.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>dbdprocurement@aff.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Department of Agriculture, Fisheries and Forestry</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>corporate.procurements@grdc.com.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Grains Research &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>cio-it-labourhire@afp.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>cdc.ict.labourhire@cdc.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>AUSTRALIAN CENTRE FOR DISEASE CONTROL</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>bilal.arshad@act.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>City and Environment Directorate</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>aidan.chalker@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>64990764@t.plcm.vc</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Aged Care Quality and Safety Commission</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
